--- a/BWI/bestwine_output/bestwine_Finland.xlsx
+++ b/BWI/bestwine_output/bestwine_Finland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA302"/>
+  <dimension ref="A1:AA311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -34583,6 +34583,923 @@
         </is>
       </c>
     </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>Wineconnection Finland</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>Wineconnection Finland</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>146104</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>13 Veistotie</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>02330</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>http://wineconnection.fi</t>
+        </is>
+      </c>
+      <c r="J303" s="2" t="inlineStr"/>
+      <c r="K303" s="2" t="inlineStr"/>
+      <c r="L303" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="inlineStr"/>
+      <c r="N303" s="2" t="inlineStr">
+        <is>
+          <t>info@wineconnection.fi</t>
+        </is>
+      </c>
+      <c r="O303" s="2" t="inlineStr"/>
+      <c r="P303" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q303" s="2" t="inlineStr">
+        <is>
+          <t>29183533</t>
+        </is>
+      </c>
+      <c r="R303" s="2" t="inlineStr"/>
+      <c r="S303" s="2" t="inlineStr">
+        <is>
+          <t>http://www.facebook.com/wineconnectionfinland/</t>
+        </is>
+      </c>
+      <c r="T303" s="2" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/wineconnectionfinland</t>
+        </is>
+      </c>
+      <c r="U303" s="2" t="inlineStr"/>
+      <c r="V303" s="2" t="inlineStr"/>
+      <c r="W303" s="2" t="inlineStr"/>
+      <c r="X303" s="2" t="inlineStr"/>
+      <c r="Y303" s="2" t="inlineStr"/>
+      <c r="Z303" s="2" t="inlineStr"/>
+      <c r="AA303" s="2" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>146099</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>24 Melkonkatu</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>00210</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.carsinandfriends.com</t>
+        </is>
+      </c>
+      <c r="J304" s="2" t="inlineStr"/>
+      <c r="K304" s="2" t="inlineStr"/>
+      <c r="L304" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="inlineStr"/>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>nea@carsin.com</t>
+        </is>
+      </c>
+      <c r="O304" s="2" t="inlineStr"/>
+      <c r="P304" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q304" s="2" t="inlineStr">
+        <is>
+          <t>31475578</t>
+        </is>
+      </c>
+      <c r="R304" s="2" t="inlineStr"/>
+      <c r="S304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/chateaucarsin</t>
+        </is>
+      </c>
+      <c r="T304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chateaucarsin/</t>
+        </is>
+      </c>
+      <c r="U304" s="2" t="inlineStr"/>
+      <c r="V304" s="2" t="inlineStr"/>
+      <c r="W304" s="2" t="inlineStr">
+        <is>
+          <t>Jukka Orasjärvi</t>
+        </is>
+      </c>
+      <c r="X304" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y304" s="2" t="inlineStr"/>
+      <c r="Z304" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA304" s="2" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>146099</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>24 Melkonkatu</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>00210</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.carsinandfriends.com</t>
+        </is>
+      </c>
+      <c r="J305" s="2" t="inlineStr"/>
+      <c r="K305" s="2" t="inlineStr"/>
+      <c r="L305" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="inlineStr"/>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>nea@carsin.com</t>
+        </is>
+      </c>
+      <c r="O305" s="2" t="inlineStr"/>
+      <c r="P305" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q305" s="2" t="inlineStr">
+        <is>
+          <t>31475578</t>
+        </is>
+      </c>
+      <c r="R305" s="2" t="inlineStr"/>
+      <c r="S305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/chateaucarsin</t>
+        </is>
+      </c>
+      <c r="T305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chateaucarsin/</t>
+        </is>
+      </c>
+      <c r="U305" s="2" t="inlineStr"/>
+      <c r="V305" s="2" t="inlineStr"/>
+      <c r="W305" s="2" t="inlineStr">
+        <is>
+          <t>Jasu Sohlberg</t>
+        </is>
+      </c>
+      <c r="X305" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y305" s="2" t="inlineStr"/>
+      <c r="Z305" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jasu-sohlberg-558388131/</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>146099</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>24 Melkonkatu</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>00210</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.carsinandfriends.com</t>
+        </is>
+      </c>
+      <c r="J306" s="2" t="inlineStr"/>
+      <c r="K306" s="2" t="inlineStr"/>
+      <c r="L306" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="inlineStr"/>
+      <c r="N306" s="2" t="inlineStr">
+        <is>
+          <t>nea@carsin.com</t>
+        </is>
+      </c>
+      <c r="O306" s="2" t="inlineStr"/>
+      <c r="P306" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q306" s="2" t="inlineStr">
+        <is>
+          <t>31475578</t>
+        </is>
+      </c>
+      <c r="R306" s="2" t="inlineStr"/>
+      <c r="S306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/chateaucarsin</t>
+        </is>
+      </c>
+      <c r="T306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chateaucarsin/</t>
+        </is>
+      </c>
+      <c r="U306" s="2" t="inlineStr"/>
+      <c r="V306" s="2" t="inlineStr"/>
+      <c r="W306" s="2" t="inlineStr">
+        <is>
+          <t>Nea Berglund</t>
+        </is>
+      </c>
+      <c r="X306" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y306" s="2" t="inlineStr"/>
+      <c r="Z306" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA306" s="2" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>Gusto Partners Oy</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>Gusto Partners Oy</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>146110</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>40 Lönnrotinkatu</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gustopartners.fi</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="inlineStr"/>
+      <c r="K307" s="2" t="inlineStr"/>
+      <c r="L307" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="inlineStr"/>
+      <c r="N307" s="2" t="inlineStr">
+        <is>
+          <t>yhteydenotot@gustopartners.fi</t>
+        </is>
+      </c>
+      <c r="O307" s="2" t="inlineStr"/>
+      <c r="P307" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q307" s="2" t="inlineStr">
+        <is>
+          <t>19928474</t>
+        </is>
+      </c>
+      <c r="R307" s="2" t="inlineStr"/>
+      <c r="S307" s="2" t="inlineStr"/>
+      <c r="T307" s="2" t="inlineStr"/>
+      <c r="U307" s="2" t="inlineStr"/>
+      <c r="V307" s="2" t="inlineStr"/>
+      <c r="W307" s="2" t="inlineStr">
+        <is>
+          <t>Kristian Blanco</t>
+        </is>
+      </c>
+      <c r="X307" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director/ Ceo</t>
+        </is>
+      </c>
+      <c r="Y307" s="2" t="inlineStr"/>
+      <c r="Z307" s="2" t="inlineStr"/>
+      <c r="AA307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kristian-blanco-sequeiros-3566992/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>Santevin Oy</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>Santevin Oy</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>146092</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>Tampere</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>Pirkanmaa</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>2 Hatanpään valtatie</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>33100</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.santevin.fi</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="inlineStr"/>
+      <c r="K308" s="2" t="inlineStr"/>
+      <c r="L308" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M308" s="2" t="inlineStr"/>
+      <c r="N308" s="2" t="inlineStr">
+        <is>
+          <t>santevin@santevin.fi</t>
+        </is>
+      </c>
+      <c r="O308" s="2" t="inlineStr"/>
+      <c r="P308" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q308" s="2" t="inlineStr">
+        <is>
+          <t>30922081</t>
+        </is>
+      </c>
+      <c r="R308" s="2" t="inlineStr"/>
+      <c r="S308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/santevinfinland/</t>
+        </is>
+      </c>
+      <c r="T308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/santevin_finland_/</t>
+        </is>
+      </c>
+      <c r="U308" s="2" t="inlineStr"/>
+      <c r="V308" s="2" t="inlineStr"/>
+      <c r="W308" s="2" t="inlineStr">
+        <is>
+          <t>Tuula Tikkanen</t>
+        </is>
+      </c>
+      <c r="X308" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y308" s="2" t="inlineStr"/>
+      <c r="Z308" s="2" t="inlineStr"/>
+      <c r="AA308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tuula-tikkanen-077502250/</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>146090</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>4 Linnanherrankuja</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>00950</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>https://potio.fi</t>
+        </is>
+      </c>
+      <c r="J309" s="2" t="inlineStr"/>
+      <c r="K309" s="2" t="inlineStr"/>
+      <c r="L309" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M309" s="2" t="inlineStr"/>
+      <c r="N309" s="2" t="inlineStr">
+        <is>
+          <t>info@potio.fi</t>
+        </is>
+      </c>
+      <c r="O309" s="2" t="inlineStr"/>
+      <c r="P309" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q309" s="2" t="inlineStr">
+        <is>
+          <t>27962314</t>
+        </is>
+      </c>
+      <c r="R309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/potio-oy/</t>
+        </is>
+      </c>
+      <c r="S309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/potiofi#</t>
+        </is>
+      </c>
+      <c r="T309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/potio_fi/</t>
+        </is>
+      </c>
+      <c r="U309" s="2" t="inlineStr"/>
+      <c r="V309" s="2" t="inlineStr"/>
+      <c r="W309" s="2" t="inlineStr">
+        <is>
+          <t>Timo Kovanen</t>
+        </is>
+      </c>
+      <c r="X309" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="Y309" s="2" t="inlineStr"/>
+      <c r="Z309" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timokovanen</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>146090</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>4 Linnanherrankuja</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>00950</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>https://potio.fi</t>
+        </is>
+      </c>
+      <c r="J310" s="2" t="inlineStr"/>
+      <c r="K310" s="2" t="inlineStr"/>
+      <c r="L310" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M310" s="2" t="inlineStr"/>
+      <c r="N310" s="2" t="inlineStr">
+        <is>
+          <t>info@potio.fi</t>
+        </is>
+      </c>
+      <c r="O310" s="2" t="inlineStr"/>
+      <c r="P310" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q310" s="2" t="inlineStr">
+        <is>
+          <t>27962314</t>
+        </is>
+      </c>
+      <c r="R310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/potio-oy/</t>
+        </is>
+      </c>
+      <c r="S310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/potiofi#</t>
+        </is>
+      </c>
+      <c r="T310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/potio_fi/</t>
+        </is>
+      </c>
+      <c r="U310" s="2" t="inlineStr"/>
+      <c r="V310" s="2" t="inlineStr"/>
+      <c r="W310" s="2" t="inlineStr">
+        <is>
+          <t>Anton Molin</t>
+        </is>
+      </c>
+      <c r="X310" s="2" t="inlineStr">
+        <is>
+          <t>Import &amp; Export</t>
+        </is>
+      </c>
+      <c r="Y310" s="2" t="inlineStr"/>
+      <c r="Z310" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anton-molin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>146090</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>4 Linnanherrankuja</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>00950</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>https://potio.fi</t>
+        </is>
+      </c>
+      <c r="J311" s="2" t="inlineStr"/>
+      <c r="K311" s="2" t="inlineStr"/>
+      <c r="L311" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="inlineStr"/>
+      <c r="N311" s="2" t="inlineStr">
+        <is>
+          <t>info@potio.fi</t>
+        </is>
+      </c>
+      <c r="O311" s="2" t="inlineStr"/>
+      <c r="P311" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q311" s="2" t="inlineStr">
+        <is>
+          <t>27962314</t>
+        </is>
+      </c>
+      <c r="R311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/potio-oy/</t>
+        </is>
+      </c>
+      <c r="S311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/potiofi#</t>
+        </is>
+      </c>
+      <c r="T311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/potio_fi/</t>
+        </is>
+      </c>
+      <c r="U311" s="2" t="inlineStr"/>
+      <c r="V311" s="2" t="inlineStr"/>
+      <c r="W311" s="2" t="inlineStr">
+        <is>
+          <t>Tom Molin</t>
+        </is>
+      </c>
+      <c r="X311" s="2" t="inlineStr">
+        <is>
+          <t>Senior Wine Director</t>
+        </is>
+      </c>
+      <c r="Y311" s="2" t="inlineStr"/>
+      <c r="Z311" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tom-molin-1162474/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Finland.xlsx
+++ b/BWI/bestwine_output/bestwine_Finland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA311"/>
+  <dimension ref="A1:AA329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -35500,6 +35500,1836 @@
         </is>
       </c>
     </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>Kaubbacom Oü</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>Kaubbacom Oü</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>146109</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>100 Mannerheimintie</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>00100</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>https://kaubba.com</t>
+        </is>
+      </c>
+      <c r="J312" s="2" t="inlineStr"/>
+      <c r="K312" s="2" t="inlineStr"/>
+      <c r="L312" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="inlineStr"/>
+      <c r="N312" s="2" t="inlineStr">
+        <is>
+          <t>info@kaubba.com</t>
+        </is>
+      </c>
+      <c r="O312" s="2" t="inlineStr"/>
+      <c r="P312" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q312" s="2" t="inlineStr">
+        <is>
+          <t>34853001</t>
+        </is>
+      </c>
+      <c r="R312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wineryorder</t>
+        </is>
+      </c>
+      <c r="S312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KAUBBAcom</t>
+        </is>
+      </c>
+      <c r="T312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kaubba_com</t>
+        </is>
+      </c>
+      <c r="U312" s="2" t="inlineStr"/>
+      <c r="V312" s="2" t="inlineStr"/>
+      <c r="W312" s="2" t="inlineStr">
+        <is>
+          <t>Timo Kovanen</t>
+        </is>
+      </c>
+      <c r="X312" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="Y312" s="2" t="inlineStr"/>
+      <c r="Z312" s="2" t="inlineStr"/>
+      <c r="AA312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timokovanen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>Kaubbacom Oü</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>Kaubbacom Oü</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>146109</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>100 Mannerheimintie</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>00100</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>https://kaubba.com</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="inlineStr"/>
+      <c r="K313" s="2" t="inlineStr"/>
+      <c r="L313" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M313" s="2" t="inlineStr"/>
+      <c r="N313" s="2" t="inlineStr">
+        <is>
+          <t>info@kaubba.com</t>
+        </is>
+      </c>
+      <c r="O313" s="2" t="inlineStr"/>
+      <c r="P313" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q313" s="2" t="inlineStr">
+        <is>
+          <t>34853001</t>
+        </is>
+      </c>
+      <c r="R313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wineryorder</t>
+        </is>
+      </c>
+      <c r="S313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KAUBBAcom</t>
+        </is>
+      </c>
+      <c r="T313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kaubba_com</t>
+        </is>
+      </c>
+      <c r="U313" s="2" t="inlineStr"/>
+      <c r="V313" s="2" t="inlineStr"/>
+      <c r="W313" s="2" t="inlineStr">
+        <is>
+          <t>Jarkko Metsomäki</t>
+        </is>
+      </c>
+      <c r="X313" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y313" s="2" t="inlineStr"/>
+      <c r="Z313" s="2" t="inlineStr"/>
+      <c r="AA313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jarkko-metsom%C3%A4ki-37214192/</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>Bubblehouse Finland Oy</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>Bubblehouse Finland Oy</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>146111</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>48 Runeberginkatu</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>00260</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bubblehouse.fi</t>
+        </is>
+      </c>
+      <c r="J314" s="2" t="inlineStr"/>
+      <c r="K314" s="2" t="inlineStr"/>
+      <c r="L314" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M314" s="2" t="inlineStr"/>
+      <c r="N314" s="2" t="inlineStr">
+        <is>
+          <t>mika@bubblehouse.fi</t>
+        </is>
+      </c>
+      <c r="O314" s="2" t="inlineStr"/>
+      <c r="P314" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q314" s="2" t="inlineStr">
+        <is>
+          <t>33515617</t>
+        </is>
+      </c>
+      <c r="R314" s="2" t="inlineStr"/>
+      <c r="S314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bubblehouse.fi</t>
+        </is>
+      </c>
+      <c r="T314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bubblehouse.fi/</t>
+        </is>
+      </c>
+      <c r="U314" s="2" t="inlineStr"/>
+      <c r="V314" s="2" t="inlineStr"/>
+      <c r="W314" s="2" t="inlineStr">
+        <is>
+          <t>Marjakangas Mika</t>
+        </is>
+      </c>
+      <c r="X314" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y314" s="2" t="inlineStr"/>
+      <c r="Z314" s="2" t="inlineStr"/>
+      <c r="AA314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mika-marjakangas-78b59067</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>Viiniateljee Oy</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>Viiniateljee Oy</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>146097</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>Turku</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>Varsinais-Suomi</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>10 Vajossuonkatu</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>20360</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.viiniateljee.fi</t>
+        </is>
+      </c>
+      <c r="J315" s="2" t="inlineStr"/>
+      <c r="K315" s="2" t="inlineStr"/>
+      <c r="L315" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M315" s="2" t="inlineStr"/>
+      <c r="N315" s="2" t="inlineStr">
+        <is>
+          <t>info@viiniateljee.fi</t>
+        </is>
+      </c>
+      <c r="O315" s="2" t="inlineStr"/>
+      <c r="P315" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q315" s="2" t="inlineStr">
+        <is>
+          <t>34391441</t>
+        </is>
+      </c>
+      <c r="R315" s="2" t="inlineStr"/>
+      <c r="S315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viiniateljee/</t>
+        </is>
+      </c>
+      <c r="T315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viiniateljee</t>
+        </is>
+      </c>
+      <c r="U315" s="2" t="inlineStr"/>
+      <c r="V315" s="2" t="inlineStr"/>
+      <c r="W315" s="2" t="inlineStr">
+        <is>
+          <t>Eklund Päivi</t>
+        </is>
+      </c>
+      <c r="X315" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y315" s="2" t="inlineStr"/>
+      <c r="Z315" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA315" s="2" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>Mrnebbiolo Oy</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>Mrnebbiolo Oy</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>146098</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>6d Kappelikuja</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>02200</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cincinvino.fi</t>
+        </is>
+      </c>
+      <c r="J316" s="2" t="inlineStr"/>
+      <c r="K316" s="2" t="inlineStr"/>
+      <c r="L316" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M316" s="2" t="inlineStr"/>
+      <c r="N316" s="2" t="inlineStr">
+        <is>
+          <t>info@nebbiolo.fi</t>
+        </is>
+      </c>
+      <c r="O316" s="2" t="inlineStr"/>
+      <c r="P316" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q316" s="2" t="inlineStr">
+        <is>
+          <t>23776135</t>
+        </is>
+      </c>
+      <c r="R316" s="2" t="inlineStr"/>
+      <c r="S316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cincinvinofinland</t>
+        </is>
+      </c>
+      <c r="T316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cincinvino</t>
+        </is>
+      </c>
+      <c r="U316" s="2" t="inlineStr"/>
+      <c r="V316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@Viinikirjeenvaihtaja</t>
+        </is>
+      </c>
+      <c r="W316" s="2" t="inlineStr">
+        <is>
+          <t>Petteri Laine</t>
+        </is>
+      </c>
+      <c r="X316" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y316" s="2" t="inlineStr"/>
+      <c r="Z316" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA316" s="2" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>Grupo Fuente Oy, Grupo Fuente Ltd</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>Grupo Fuente Oy, Grupo Fuente Ltd</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>146114</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>1 Hakamaankuja</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>02120</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>https://grupofuente.fi</t>
+        </is>
+      </c>
+      <c r="J317" s="2" t="inlineStr"/>
+      <c r="K317" s="2" t="inlineStr"/>
+      <c r="L317" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M317" s="2" t="inlineStr"/>
+      <c r="N317" s="2" t="inlineStr">
+        <is>
+          <t>timo@grupofuente.fi</t>
+        </is>
+      </c>
+      <c r="O317" s="2" t="inlineStr"/>
+      <c r="P317" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q317" s="2" t="inlineStr">
+        <is>
+          <t>32479327</t>
+        </is>
+      </c>
+      <c r="R317" s="2" t="inlineStr"/>
+      <c r="S317" s="2" t="inlineStr"/>
+      <c r="T317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grupofuente.fi/</t>
+        </is>
+      </c>
+      <c r="U317" s="2" t="inlineStr"/>
+      <c r="V317" s="2" t="inlineStr"/>
+      <c r="W317" s="2" t="inlineStr">
+        <is>
+          <t>Helena Partanen</t>
+        </is>
+      </c>
+      <c r="X317" s="2" t="inlineStr">
+        <is>
+          <t>Chairman of the Board</t>
+        </is>
+      </c>
+      <c r="Y317" s="2" t="inlineStr"/>
+      <c r="Z317" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA317" s="2" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>Grupo Fuente Oy, Grupo Fuente Ltd</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>Grupo Fuente Oy, Grupo Fuente Ltd</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>146114</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>1 Hakamaankuja</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>02120</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>https://grupofuente.fi</t>
+        </is>
+      </c>
+      <c r="J318" s="2" t="inlineStr"/>
+      <c r="K318" s="2" t="inlineStr"/>
+      <c r="L318" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M318" s="2" t="inlineStr"/>
+      <c r="N318" s="2" t="inlineStr">
+        <is>
+          <t>timo@grupofuente.fi</t>
+        </is>
+      </c>
+      <c r="O318" s="2" t="inlineStr"/>
+      <c r="P318" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q318" s="2" t="inlineStr">
+        <is>
+          <t>32479327</t>
+        </is>
+      </c>
+      <c r="R318" s="2" t="inlineStr"/>
+      <c r="S318" s="2" t="inlineStr"/>
+      <c r="T318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grupofuente.fi/</t>
+        </is>
+      </c>
+      <c r="U318" s="2" t="inlineStr"/>
+      <c r="V318" s="2" t="inlineStr"/>
+      <c r="W318" s="2" t="inlineStr">
+        <is>
+          <t>Timo Partanen</t>
+        </is>
+      </c>
+      <c r="X318" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y318" s="2" t="inlineStr"/>
+      <c r="Z318" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA318" s="2" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>Just Drinks Oy</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>Just Drinks Oy</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>146105</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>11a Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>https://justdrinks.fi</t>
+        </is>
+      </c>
+      <c r="J319" s="2" t="inlineStr"/>
+      <c r="K319" s="2" t="inlineStr"/>
+      <c r="L319" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M319" s="2" t="inlineStr"/>
+      <c r="N319" s="2" t="inlineStr">
+        <is>
+          <t>contact@justdrinks.fi</t>
+        </is>
+      </c>
+      <c r="O319" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 000000</t>
+        </is>
+      </c>
+      <c r="P319" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q319" s="2" t="inlineStr">
+        <is>
+          <t>23744045</t>
+        </is>
+      </c>
+      <c r="R319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/just-drinks-finland/</t>
+        </is>
+      </c>
+      <c r="S319" s="2" t="inlineStr"/>
+      <c r="T319" s="2" t="inlineStr"/>
+      <c r="U319" s="2" t="inlineStr"/>
+      <c r="V319" s="2" t="inlineStr"/>
+      <c r="W319" s="2" t="inlineStr">
+        <is>
+          <t>Michael Grönfors</t>
+        </is>
+      </c>
+      <c r="X319" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y319" s="2" t="inlineStr"/>
+      <c r="Z319" s="2" t="inlineStr"/>
+      <c r="AA319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michael-gr%C3%B6nfors-b62a8468/</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>Just Drinks Oy</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>Just Drinks Oy</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>146105</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>11a Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>https://justdrinks.fi</t>
+        </is>
+      </c>
+      <c r="J320" s="2" t="inlineStr"/>
+      <c r="K320" s="2" t="inlineStr"/>
+      <c r="L320" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M320" s="2" t="inlineStr"/>
+      <c r="N320" s="2" t="inlineStr">
+        <is>
+          <t>contact@justdrinks.fi</t>
+        </is>
+      </c>
+      <c r="O320" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 000000</t>
+        </is>
+      </c>
+      <c r="P320" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q320" s="2" t="inlineStr">
+        <is>
+          <t>23744045</t>
+        </is>
+      </c>
+      <c r="R320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/just-drinks-finland/</t>
+        </is>
+      </c>
+      <c r="S320" s="2" t="inlineStr"/>
+      <c r="T320" s="2" t="inlineStr"/>
+      <c r="U320" s="2" t="inlineStr"/>
+      <c r="V320" s="2" t="inlineStr"/>
+      <c r="W320" s="2" t="inlineStr">
+        <is>
+          <t>Emmi Helppi</t>
+        </is>
+      </c>
+      <c r="X320" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y320" s="2" t="inlineStr"/>
+      <c r="Z320" s="2" t="inlineStr"/>
+      <c r="AA320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emmi-helppi-former-kokko-09aa4a37/</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>Wineconnection Finland</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>Wineconnection Finland</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>146104</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>13 Veistotie</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>02330</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>http://wineconnection.fi</t>
+        </is>
+      </c>
+      <c r="J321" s="2" t="inlineStr"/>
+      <c r="K321" s="2" t="inlineStr"/>
+      <c r="L321" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M321" s="2" t="inlineStr"/>
+      <c r="N321" s="2" t="inlineStr">
+        <is>
+          <t>info@wineconnection.fi</t>
+        </is>
+      </c>
+      <c r="O321" s="2" t="inlineStr"/>
+      <c r="P321" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q321" s="2" t="inlineStr">
+        <is>
+          <t>29183533</t>
+        </is>
+      </c>
+      <c r="R321" s="2" t="inlineStr"/>
+      <c r="S321" s="2" t="inlineStr">
+        <is>
+          <t>http://www.facebook.com/wineconnectionfinland/</t>
+        </is>
+      </c>
+      <c r="T321" s="2" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/wineconnectionfinland</t>
+        </is>
+      </c>
+      <c r="U321" s="2" t="inlineStr"/>
+      <c r="V321" s="2" t="inlineStr"/>
+      <c r="W321" s="2" t="inlineStr"/>
+      <c r="X321" s="2" t="inlineStr"/>
+      <c r="Y321" s="2" t="inlineStr"/>
+      <c r="Z321" s="2" t="inlineStr"/>
+      <c r="AA321" s="2" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>146099</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>24 Melkonkatu</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>00210</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.carsinandfriends.com</t>
+        </is>
+      </c>
+      <c r="J322" s="2" t="inlineStr"/>
+      <c r="K322" s="2" t="inlineStr"/>
+      <c r="L322" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M322" s="2" t="inlineStr"/>
+      <c r="N322" s="2" t="inlineStr">
+        <is>
+          <t>nea@carsin.com</t>
+        </is>
+      </c>
+      <c r="O322" s="2" t="inlineStr"/>
+      <c r="P322" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q322" s="2" t="inlineStr">
+        <is>
+          <t>31475578</t>
+        </is>
+      </c>
+      <c r="R322" s="2" t="inlineStr"/>
+      <c r="S322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/chateaucarsin</t>
+        </is>
+      </c>
+      <c r="T322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chateaucarsin/</t>
+        </is>
+      </c>
+      <c r="U322" s="2" t="inlineStr"/>
+      <c r="V322" s="2" t="inlineStr"/>
+      <c r="W322" s="2" t="inlineStr">
+        <is>
+          <t>Jukka Orasjärvi</t>
+        </is>
+      </c>
+      <c r="X322" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y322" s="2" t="inlineStr"/>
+      <c r="Z322" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA322" s="2" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>146099</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>24 Melkonkatu</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>00210</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.carsinandfriends.com</t>
+        </is>
+      </c>
+      <c r="J323" s="2" t="inlineStr"/>
+      <c r="K323" s="2" t="inlineStr"/>
+      <c r="L323" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M323" s="2" t="inlineStr"/>
+      <c r="N323" s="2" t="inlineStr">
+        <is>
+          <t>nea@carsin.com</t>
+        </is>
+      </c>
+      <c r="O323" s="2" t="inlineStr"/>
+      <c r="P323" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q323" s="2" t="inlineStr">
+        <is>
+          <t>31475578</t>
+        </is>
+      </c>
+      <c r="R323" s="2" t="inlineStr"/>
+      <c r="S323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/chateaucarsin</t>
+        </is>
+      </c>
+      <c r="T323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chateaucarsin/</t>
+        </is>
+      </c>
+      <c r="U323" s="2" t="inlineStr"/>
+      <c r="V323" s="2" t="inlineStr"/>
+      <c r="W323" s="2" t="inlineStr">
+        <is>
+          <t>Jasu Sohlberg</t>
+        </is>
+      </c>
+      <c r="X323" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y323" s="2" t="inlineStr"/>
+      <c r="Z323" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jasu-sohlberg-558388131/</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>146099</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>24 Melkonkatu</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>00210</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.carsinandfriends.com</t>
+        </is>
+      </c>
+      <c r="J324" s="2" t="inlineStr"/>
+      <c r="K324" s="2" t="inlineStr"/>
+      <c r="L324" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M324" s="2" t="inlineStr"/>
+      <c r="N324" s="2" t="inlineStr">
+        <is>
+          <t>nea@carsin.com</t>
+        </is>
+      </c>
+      <c r="O324" s="2" t="inlineStr"/>
+      <c r="P324" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q324" s="2" t="inlineStr">
+        <is>
+          <t>31475578</t>
+        </is>
+      </c>
+      <c r="R324" s="2" t="inlineStr"/>
+      <c r="S324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/chateaucarsin</t>
+        </is>
+      </c>
+      <c r="T324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chateaucarsin/</t>
+        </is>
+      </c>
+      <c r="U324" s="2" t="inlineStr"/>
+      <c r="V324" s="2" t="inlineStr"/>
+      <c r="W324" s="2" t="inlineStr">
+        <is>
+          <t>Nea Berglund</t>
+        </is>
+      </c>
+      <c r="X324" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y324" s="2" t="inlineStr"/>
+      <c r="Z324" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA324" s="2" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>Gusto Partners Oy</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>Gusto Partners Oy</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>146110</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>40 Lönnrotinkatu</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gustopartners.fi</t>
+        </is>
+      </c>
+      <c r="J325" s="2" t="inlineStr"/>
+      <c r="K325" s="2" t="inlineStr"/>
+      <c r="L325" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M325" s="2" t="inlineStr"/>
+      <c r="N325" s="2" t="inlineStr">
+        <is>
+          <t>yhteydenotot@gustopartners.fi</t>
+        </is>
+      </c>
+      <c r="O325" s="2" t="inlineStr"/>
+      <c r="P325" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q325" s="2" t="inlineStr">
+        <is>
+          <t>19928474</t>
+        </is>
+      </c>
+      <c r="R325" s="2" t="inlineStr"/>
+      <c r="S325" s="2" t="inlineStr"/>
+      <c r="T325" s="2" t="inlineStr"/>
+      <c r="U325" s="2" t="inlineStr"/>
+      <c r="V325" s="2" t="inlineStr"/>
+      <c r="W325" s="2" t="inlineStr">
+        <is>
+          <t>Kristian Blanco</t>
+        </is>
+      </c>
+      <c r="X325" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director/ Ceo</t>
+        </is>
+      </c>
+      <c r="Y325" s="2" t="inlineStr"/>
+      <c r="Z325" s="2" t="inlineStr"/>
+      <c r="AA325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kristian-blanco-sequeiros-3566992/</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>Santevin Oy</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>Santevin Oy</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>146092</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>Tampere</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>Pirkanmaa</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>2 Hatanpään valtatie</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>33100</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.santevin.fi</t>
+        </is>
+      </c>
+      <c r="J326" s="2" t="inlineStr"/>
+      <c r="K326" s="2" t="inlineStr"/>
+      <c r="L326" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M326" s="2" t="inlineStr"/>
+      <c r="N326" s="2" t="inlineStr">
+        <is>
+          <t>santevin@santevin.fi</t>
+        </is>
+      </c>
+      <c r="O326" s="2" t="inlineStr"/>
+      <c r="P326" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q326" s="2" t="inlineStr">
+        <is>
+          <t>30922081</t>
+        </is>
+      </c>
+      <c r="R326" s="2" t="inlineStr"/>
+      <c r="S326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/santevinfinland/</t>
+        </is>
+      </c>
+      <c r="T326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/santevin_finland_/</t>
+        </is>
+      </c>
+      <c r="U326" s="2" t="inlineStr"/>
+      <c r="V326" s="2" t="inlineStr"/>
+      <c r="W326" s="2" t="inlineStr">
+        <is>
+          <t>Tuula Tikkanen</t>
+        </is>
+      </c>
+      <c r="X326" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y326" s="2" t="inlineStr"/>
+      <c r="Z326" s="2" t="inlineStr"/>
+      <c r="AA326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tuula-tikkanen-077502250/</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>146090</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>4 Linnanherrankuja</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>00950</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>https://potio.fi</t>
+        </is>
+      </c>
+      <c r="J327" s="2" t="inlineStr"/>
+      <c r="K327" s="2" t="inlineStr"/>
+      <c r="L327" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M327" s="2" t="inlineStr"/>
+      <c r="N327" s="2" t="inlineStr">
+        <is>
+          <t>info@potio.fi</t>
+        </is>
+      </c>
+      <c r="O327" s="2" t="inlineStr"/>
+      <c r="P327" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q327" s="2" t="inlineStr">
+        <is>
+          <t>27962314</t>
+        </is>
+      </c>
+      <c r="R327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/potio-oy/</t>
+        </is>
+      </c>
+      <c r="S327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/potiofi#</t>
+        </is>
+      </c>
+      <c r="T327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/potio_fi/</t>
+        </is>
+      </c>
+      <c r="U327" s="2" t="inlineStr"/>
+      <c r="V327" s="2" t="inlineStr"/>
+      <c r="W327" s="2" t="inlineStr">
+        <is>
+          <t>Timo Kovanen</t>
+        </is>
+      </c>
+      <c r="X327" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="Y327" s="2" t="inlineStr"/>
+      <c r="Z327" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timokovanen</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>146090</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>4 Linnanherrankuja</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>00950</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>https://potio.fi</t>
+        </is>
+      </c>
+      <c r="J328" s="2" t="inlineStr"/>
+      <c r="K328" s="2" t="inlineStr"/>
+      <c r="L328" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M328" s="2" t="inlineStr"/>
+      <c r="N328" s="2" t="inlineStr">
+        <is>
+          <t>info@potio.fi</t>
+        </is>
+      </c>
+      <c r="O328" s="2" t="inlineStr"/>
+      <c r="P328" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q328" s="2" t="inlineStr">
+        <is>
+          <t>27962314</t>
+        </is>
+      </c>
+      <c r="R328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/potio-oy/</t>
+        </is>
+      </c>
+      <c r="S328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/potiofi#</t>
+        </is>
+      </c>
+      <c r="T328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/potio_fi/</t>
+        </is>
+      </c>
+      <c r="U328" s="2" t="inlineStr"/>
+      <c r="V328" s="2" t="inlineStr"/>
+      <c r="W328" s="2" t="inlineStr">
+        <is>
+          <t>Anton Molin</t>
+        </is>
+      </c>
+      <c r="X328" s="2" t="inlineStr">
+        <is>
+          <t>Import &amp; Export</t>
+        </is>
+      </c>
+      <c r="Y328" s="2" t="inlineStr"/>
+      <c r="Z328" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anton-molin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>146090</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>4 Linnanherrankuja</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>00950</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>https://potio.fi</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="inlineStr"/>
+      <c r="K329" s="2" t="inlineStr"/>
+      <c r="L329" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M329" s="2" t="inlineStr"/>
+      <c r="N329" s="2" t="inlineStr">
+        <is>
+          <t>info@potio.fi</t>
+        </is>
+      </c>
+      <c r="O329" s="2" t="inlineStr"/>
+      <c r="P329" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q329" s="2" t="inlineStr">
+        <is>
+          <t>27962314</t>
+        </is>
+      </c>
+      <c r="R329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/potio-oy/</t>
+        </is>
+      </c>
+      <c r="S329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/potiofi#</t>
+        </is>
+      </c>
+      <c r="T329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/potio_fi/</t>
+        </is>
+      </c>
+      <c r="U329" s="2" t="inlineStr"/>
+      <c r="V329" s="2" t="inlineStr"/>
+      <c r="W329" s="2" t="inlineStr">
+        <is>
+          <t>Tom Molin</t>
+        </is>
+      </c>
+      <c r="X329" s="2" t="inlineStr">
+        <is>
+          <t>Senior Wine Director</t>
+        </is>
+      </c>
+      <c r="Y329" s="2" t="inlineStr"/>
+      <c r="Z329" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tom-molin-1162474/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Finland.xlsx
+++ b/BWI/bestwine_output/bestwine_Finland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA329"/>
+  <dimension ref="A1:AA347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -37330,6 +37330,1836 @@
         </is>
       </c>
     </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>Kaubbacom Oü</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>Kaubbacom Oü</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>146109</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>100 Mannerheimintie</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>00100</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>https://kaubba.com</t>
+        </is>
+      </c>
+      <c r="J330" s="2" t="inlineStr"/>
+      <c r="K330" s="2" t="inlineStr"/>
+      <c r="L330" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M330" s="2" t="inlineStr"/>
+      <c r="N330" s="2" t="inlineStr">
+        <is>
+          <t>info@kaubba.com</t>
+        </is>
+      </c>
+      <c r="O330" s="2" t="inlineStr"/>
+      <c r="P330" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q330" s="2" t="inlineStr">
+        <is>
+          <t>34853001</t>
+        </is>
+      </c>
+      <c r="R330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wineryorder</t>
+        </is>
+      </c>
+      <c r="S330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KAUBBAcom</t>
+        </is>
+      </c>
+      <c r="T330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kaubba_com</t>
+        </is>
+      </c>
+      <c r="U330" s="2" t="inlineStr"/>
+      <c r="V330" s="2" t="inlineStr"/>
+      <c r="W330" s="2" t="inlineStr">
+        <is>
+          <t>Timo Kovanen</t>
+        </is>
+      </c>
+      <c r="X330" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="Y330" s="2" t="inlineStr"/>
+      <c r="Z330" s="2" t="inlineStr"/>
+      <c r="AA330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timokovanen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>Kaubbacom Oü</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>Kaubbacom Oü</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>146109</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>100 Mannerheimintie</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>00100</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>https://kaubba.com</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="inlineStr"/>
+      <c r="K331" s="2" t="inlineStr"/>
+      <c r="L331" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M331" s="2" t="inlineStr"/>
+      <c r="N331" s="2" t="inlineStr">
+        <is>
+          <t>info@kaubba.com</t>
+        </is>
+      </c>
+      <c r="O331" s="2" t="inlineStr"/>
+      <c r="P331" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q331" s="2" t="inlineStr">
+        <is>
+          <t>34853001</t>
+        </is>
+      </c>
+      <c r="R331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wineryorder</t>
+        </is>
+      </c>
+      <c r="S331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KAUBBAcom</t>
+        </is>
+      </c>
+      <c r="T331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kaubba_com</t>
+        </is>
+      </c>
+      <c r="U331" s="2" t="inlineStr"/>
+      <c r="V331" s="2" t="inlineStr"/>
+      <c r="W331" s="2" t="inlineStr">
+        <is>
+          <t>Jarkko Metsomäki</t>
+        </is>
+      </c>
+      <c r="X331" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y331" s="2" t="inlineStr"/>
+      <c r="Z331" s="2" t="inlineStr"/>
+      <c r="AA331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jarkko-metsom%C3%A4ki-37214192/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>Bubblehouse Finland Oy</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>Bubblehouse Finland Oy</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>146111</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>48 Runeberginkatu</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>00260</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bubblehouse.fi</t>
+        </is>
+      </c>
+      <c r="J332" s="2" t="inlineStr"/>
+      <c r="K332" s="2" t="inlineStr"/>
+      <c r="L332" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M332" s="2" t="inlineStr"/>
+      <c r="N332" s="2" t="inlineStr">
+        <is>
+          <t>mika@bubblehouse.fi</t>
+        </is>
+      </c>
+      <c r="O332" s="2" t="inlineStr"/>
+      <c r="P332" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q332" s="2" t="inlineStr">
+        <is>
+          <t>33515617</t>
+        </is>
+      </c>
+      <c r="R332" s="2" t="inlineStr"/>
+      <c r="S332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bubblehouse.fi</t>
+        </is>
+      </c>
+      <c r="T332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bubblehouse.fi/</t>
+        </is>
+      </c>
+      <c r="U332" s="2" t="inlineStr"/>
+      <c r="V332" s="2" t="inlineStr"/>
+      <c r="W332" s="2" t="inlineStr">
+        <is>
+          <t>Marjakangas Mika</t>
+        </is>
+      </c>
+      <c r="X332" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y332" s="2" t="inlineStr"/>
+      <c r="Z332" s="2" t="inlineStr"/>
+      <c r="AA332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mika-marjakangas-78b59067</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>Viiniateljee Oy</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>Viiniateljee Oy</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>146097</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>Turku</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>Varsinais-Suomi</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>10 Vajossuonkatu</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>20360</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.viiniateljee.fi</t>
+        </is>
+      </c>
+      <c r="J333" s="2" t="inlineStr"/>
+      <c r="K333" s="2" t="inlineStr"/>
+      <c r="L333" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M333" s="2" t="inlineStr"/>
+      <c r="N333" s="2" t="inlineStr">
+        <is>
+          <t>info@viiniateljee.fi</t>
+        </is>
+      </c>
+      <c r="O333" s="2" t="inlineStr"/>
+      <c r="P333" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q333" s="2" t="inlineStr">
+        <is>
+          <t>34391441</t>
+        </is>
+      </c>
+      <c r="R333" s="2" t="inlineStr"/>
+      <c r="S333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viiniateljee/</t>
+        </is>
+      </c>
+      <c r="T333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viiniateljee</t>
+        </is>
+      </c>
+      <c r="U333" s="2" t="inlineStr"/>
+      <c r="V333" s="2" t="inlineStr"/>
+      <c r="W333" s="2" t="inlineStr">
+        <is>
+          <t>Eklund Päivi</t>
+        </is>
+      </c>
+      <c r="X333" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y333" s="2" t="inlineStr"/>
+      <c r="Z333" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA333" s="2" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>Mrnebbiolo Oy</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>Mrnebbiolo Oy</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>146098</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>6d Kappelikuja</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>02200</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cincinvino.fi</t>
+        </is>
+      </c>
+      <c r="J334" s="2" t="inlineStr"/>
+      <c r="K334" s="2" t="inlineStr"/>
+      <c r="L334" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M334" s="2" t="inlineStr"/>
+      <c r="N334" s="2" t="inlineStr">
+        <is>
+          <t>info@nebbiolo.fi</t>
+        </is>
+      </c>
+      <c r="O334" s="2" t="inlineStr"/>
+      <c r="P334" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q334" s="2" t="inlineStr">
+        <is>
+          <t>23776135</t>
+        </is>
+      </c>
+      <c r="R334" s="2" t="inlineStr"/>
+      <c r="S334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cincinvinofinland</t>
+        </is>
+      </c>
+      <c r="T334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cincinvino</t>
+        </is>
+      </c>
+      <c r="U334" s="2" t="inlineStr"/>
+      <c r="V334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@Viinikirjeenvaihtaja</t>
+        </is>
+      </c>
+      <c r="W334" s="2" t="inlineStr">
+        <is>
+          <t>Petteri Laine</t>
+        </is>
+      </c>
+      <c r="X334" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y334" s="2" t="inlineStr"/>
+      <c r="Z334" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA334" s="2" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>Grupo Fuente Oy, Grupo Fuente Ltd</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>Grupo Fuente Oy, Grupo Fuente Ltd</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>146114</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>1 Hakamaankuja</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>02120</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>https://grupofuente.fi</t>
+        </is>
+      </c>
+      <c r="J335" s="2" t="inlineStr"/>
+      <c r="K335" s="2" t="inlineStr"/>
+      <c r="L335" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M335" s="2" t="inlineStr"/>
+      <c r="N335" s="2" t="inlineStr">
+        <is>
+          <t>timo@grupofuente.fi</t>
+        </is>
+      </c>
+      <c r="O335" s="2" t="inlineStr"/>
+      <c r="P335" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q335" s="2" t="inlineStr">
+        <is>
+          <t>32479327</t>
+        </is>
+      </c>
+      <c r="R335" s="2" t="inlineStr"/>
+      <c r="S335" s="2" t="inlineStr"/>
+      <c r="T335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grupofuente.fi/</t>
+        </is>
+      </c>
+      <c r="U335" s="2" t="inlineStr"/>
+      <c r="V335" s="2" t="inlineStr"/>
+      <c r="W335" s="2" t="inlineStr">
+        <is>
+          <t>Helena Partanen</t>
+        </is>
+      </c>
+      <c r="X335" s="2" t="inlineStr">
+        <is>
+          <t>Chairman of the Board</t>
+        </is>
+      </c>
+      <c r="Y335" s="2" t="inlineStr"/>
+      <c r="Z335" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA335" s="2" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>Grupo Fuente Oy, Grupo Fuente Ltd</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>Grupo Fuente Oy, Grupo Fuente Ltd</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>146114</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>1 Hakamaankuja</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>02120</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="inlineStr">
+        <is>
+          <t>https://grupofuente.fi</t>
+        </is>
+      </c>
+      <c r="J336" s="2" t="inlineStr"/>
+      <c r="K336" s="2" t="inlineStr"/>
+      <c r="L336" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M336" s="2" t="inlineStr"/>
+      <c r="N336" s="2" t="inlineStr">
+        <is>
+          <t>timo@grupofuente.fi</t>
+        </is>
+      </c>
+      <c r="O336" s="2" t="inlineStr"/>
+      <c r="P336" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q336" s="2" t="inlineStr">
+        <is>
+          <t>32479327</t>
+        </is>
+      </c>
+      <c r="R336" s="2" t="inlineStr"/>
+      <c r="S336" s="2" t="inlineStr"/>
+      <c r="T336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grupofuente.fi/</t>
+        </is>
+      </c>
+      <c r="U336" s="2" t="inlineStr"/>
+      <c r="V336" s="2" t="inlineStr"/>
+      <c r="W336" s="2" t="inlineStr">
+        <is>
+          <t>Timo Partanen</t>
+        </is>
+      </c>
+      <c r="X336" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y336" s="2" t="inlineStr"/>
+      <c r="Z336" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA336" s="2" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>Just Drinks Oy</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>Just Drinks Oy</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>146105</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>11a Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t>https://justdrinks.fi</t>
+        </is>
+      </c>
+      <c r="J337" s="2" t="inlineStr"/>
+      <c r="K337" s="2" t="inlineStr"/>
+      <c r="L337" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M337" s="2" t="inlineStr"/>
+      <c r="N337" s="2" t="inlineStr">
+        <is>
+          <t>contact@justdrinks.fi</t>
+        </is>
+      </c>
+      <c r="O337" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 000000</t>
+        </is>
+      </c>
+      <c r="P337" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q337" s="2" t="inlineStr">
+        <is>
+          <t>23744045</t>
+        </is>
+      </c>
+      <c r="R337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/just-drinks-finland/</t>
+        </is>
+      </c>
+      <c r="S337" s="2" t="inlineStr"/>
+      <c r="T337" s="2" t="inlineStr"/>
+      <c r="U337" s="2" t="inlineStr"/>
+      <c r="V337" s="2" t="inlineStr"/>
+      <c r="W337" s="2" t="inlineStr">
+        <is>
+          <t>Michael Grönfors</t>
+        </is>
+      </c>
+      <c r="X337" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y337" s="2" t="inlineStr"/>
+      <c r="Z337" s="2" t="inlineStr"/>
+      <c r="AA337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michael-gr%C3%B6nfors-b62a8468/</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>Just Drinks Oy</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>Just Drinks Oy</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>146105</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>11a Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>https://justdrinks.fi</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="inlineStr"/>
+      <c r="K338" s="2" t="inlineStr"/>
+      <c r="L338" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M338" s="2" t="inlineStr"/>
+      <c r="N338" s="2" t="inlineStr">
+        <is>
+          <t>contact@justdrinks.fi</t>
+        </is>
+      </c>
+      <c r="O338" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 000000</t>
+        </is>
+      </c>
+      <c r="P338" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q338" s="2" t="inlineStr">
+        <is>
+          <t>23744045</t>
+        </is>
+      </c>
+      <c r="R338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/just-drinks-finland/</t>
+        </is>
+      </c>
+      <c r="S338" s="2" t="inlineStr"/>
+      <c r="T338" s="2" t="inlineStr"/>
+      <c r="U338" s="2" t="inlineStr"/>
+      <c r="V338" s="2" t="inlineStr"/>
+      <c r="W338" s="2" t="inlineStr">
+        <is>
+          <t>Emmi Helppi</t>
+        </is>
+      </c>
+      <c r="X338" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y338" s="2" t="inlineStr"/>
+      <c r="Z338" s="2" t="inlineStr"/>
+      <c r="AA338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emmi-helppi-former-kokko-09aa4a37/</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>Wineconnection Finland</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>Wineconnection Finland</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>146104</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>13 Veistotie</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>02330</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>http://wineconnection.fi</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="inlineStr"/>
+      <c r="K339" s="2" t="inlineStr"/>
+      <c r="L339" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M339" s="2" t="inlineStr"/>
+      <c r="N339" s="2" t="inlineStr">
+        <is>
+          <t>info@wineconnection.fi</t>
+        </is>
+      </c>
+      <c r="O339" s="2" t="inlineStr"/>
+      <c r="P339" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q339" s="2" t="inlineStr">
+        <is>
+          <t>29183533</t>
+        </is>
+      </c>
+      <c r="R339" s="2" t="inlineStr"/>
+      <c r="S339" s="2" t="inlineStr">
+        <is>
+          <t>http://www.facebook.com/wineconnectionfinland/</t>
+        </is>
+      </c>
+      <c r="T339" s="2" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/wineconnectionfinland</t>
+        </is>
+      </c>
+      <c r="U339" s="2" t="inlineStr"/>
+      <c r="V339" s="2" t="inlineStr"/>
+      <c r="W339" s="2" t="inlineStr"/>
+      <c r="X339" s="2" t="inlineStr"/>
+      <c r="Y339" s="2" t="inlineStr"/>
+      <c r="Z339" s="2" t="inlineStr"/>
+      <c r="AA339" s="2" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>146099</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>24 Melkonkatu</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>00210</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.carsinandfriends.com</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr"/>
+      <c r="K340" s="2" t="inlineStr"/>
+      <c r="L340" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M340" s="2" t="inlineStr"/>
+      <c r="N340" s="2" t="inlineStr">
+        <is>
+          <t>nea@carsin.com</t>
+        </is>
+      </c>
+      <c r="O340" s="2" t="inlineStr"/>
+      <c r="P340" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q340" s="2" t="inlineStr">
+        <is>
+          <t>31475578</t>
+        </is>
+      </c>
+      <c r="R340" s="2" t="inlineStr"/>
+      <c r="S340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/chateaucarsin</t>
+        </is>
+      </c>
+      <c r="T340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chateaucarsin/</t>
+        </is>
+      </c>
+      <c r="U340" s="2" t="inlineStr"/>
+      <c r="V340" s="2" t="inlineStr"/>
+      <c r="W340" s="2" t="inlineStr">
+        <is>
+          <t>Jukka Orasjärvi</t>
+        </is>
+      </c>
+      <c r="X340" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y340" s="2" t="inlineStr"/>
+      <c r="Z340" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA340" s="2" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>146099</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>24 Melkonkatu</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>00210</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.carsinandfriends.com</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr"/>
+      <c r="K341" s="2" t="inlineStr"/>
+      <c r="L341" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M341" s="2" t="inlineStr"/>
+      <c r="N341" s="2" t="inlineStr">
+        <is>
+          <t>nea@carsin.com</t>
+        </is>
+      </c>
+      <c r="O341" s="2" t="inlineStr"/>
+      <c r="P341" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q341" s="2" t="inlineStr">
+        <is>
+          <t>31475578</t>
+        </is>
+      </c>
+      <c r="R341" s="2" t="inlineStr"/>
+      <c r="S341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/chateaucarsin</t>
+        </is>
+      </c>
+      <c r="T341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chateaucarsin/</t>
+        </is>
+      </c>
+      <c r="U341" s="2" t="inlineStr"/>
+      <c r="V341" s="2" t="inlineStr"/>
+      <c r="W341" s="2" t="inlineStr">
+        <is>
+          <t>Jasu Sohlberg</t>
+        </is>
+      </c>
+      <c r="X341" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y341" s="2" t="inlineStr"/>
+      <c r="Z341" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jasu-sohlberg-558388131/</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>Carsin &amp; Friends Oy</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>146099</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>24 Melkonkatu</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>00210</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.carsinandfriends.com</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="inlineStr"/>
+      <c r="K342" s="2" t="inlineStr"/>
+      <c r="L342" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M342" s="2" t="inlineStr"/>
+      <c r="N342" s="2" t="inlineStr">
+        <is>
+          <t>nea@carsin.com</t>
+        </is>
+      </c>
+      <c r="O342" s="2" t="inlineStr"/>
+      <c r="P342" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q342" s="2" t="inlineStr">
+        <is>
+          <t>31475578</t>
+        </is>
+      </c>
+      <c r="R342" s="2" t="inlineStr"/>
+      <c r="S342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/chateaucarsin</t>
+        </is>
+      </c>
+      <c r="T342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chateaucarsin/</t>
+        </is>
+      </c>
+      <c r="U342" s="2" t="inlineStr"/>
+      <c r="V342" s="2" t="inlineStr"/>
+      <c r="W342" s="2" t="inlineStr">
+        <is>
+          <t>Nea Berglund</t>
+        </is>
+      </c>
+      <c r="X342" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y342" s="2" t="inlineStr"/>
+      <c r="Z342" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA342" s="2" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>Gusto Partners Oy</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>Gusto Partners Oy</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>146110</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>40 Lönnrotinkatu</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gustopartners.fi</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="inlineStr"/>
+      <c r="K343" s="2" t="inlineStr"/>
+      <c r="L343" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M343" s="2" t="inlineStr"/>
+      <c r="N343" s="2" t="inlineStr">
+        <is>
+          <t>yhteydenotot@gustopartners.fi</t>
+        </is>
+      </c>
+      <c r="O343" s="2" t="inlineStr"/>
+      <c r="P343" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q343" s="2" t="inlineStr">
+        <is>
+          <t>19928474</t>
+        </is>
+      </c>
+      <c r="R343" s="2" t="inlineStr"/>
+      <c r="S343" s="2" t="inlineStr"/>
+      <c r="T343" s="2" t="inlineStr"/>
+      <c r="U343" s="2" t="inlineStr"/>
+      <c r="V343" s="2" t="inlineStr"/>
+      <c r="W343" s="2" t="inlineStr">
+        <is>
+          <t>Kristian Blanco</t>
+        </is>
+      </c>
+      <c r="X343" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director/ Ceo</t>
+        </is>
+      </c>
+      <c r="Y343" s="2" t="inlineStr"/>
+      <c r="Z343" s="2" t="inlineStr"/>
+      <c r="AA343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kristian-blanco-sequeiros-3566992/</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>Santevin Oy</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>Santevin Oy</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>146092</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>Tampere</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>Pirkanmaa</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>2 Hatanpään valtatie</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>33100</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.santevin.fi</t>
+        </is>
+      </c>
+      <c r="J344" s="2" t="inlineStr"/>
+      <c r="K344" s="2" t="inlineStr"/>
+      <c r="L344" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M344" s="2" t="inlineStr"/>
+      <c r="N344" s="2" t="inlineStr">
+        <is>
+          <t>santevin@santevin.fi</t>
+        </is>
+      </c>
+      <c r="O344" s="2" t="inlineStr"/>
+      <c r="P344" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q344" s="2" t="inlineStr">
+        <is>
+          <t>30922081</t>
+        </is>
+      </c>
+      <c r="R344" s="2" t="inlineStr"/>
+      <c r="S344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/santevinfinland/</t>
+        </is>
+      </c>
+      <c r="T344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/santevin_finland_/</t>
+        </is>
+      </c>
+      <c r="U344" s="2" t="inlineStr"/>
+      <c r="V344" s="2" t="inlineStr"/>
+      <c r="W344" s="2" t="inlineStr">
+        <is>
+          <t>Tuula Tikkanen</t>
+        </is>
+      </c>
+      <c r="X344" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y344" s="2" t="inlineStr"/>
+      <c r="Z344" s="2" t="inlineStr"/>
+      <c r="AA344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tuula-tikkanen-077502250/</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>146090</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>4 Linnanherrankuja</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>00950</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>https://potio.fi</t>
+        </is>
+      </c>
+      <c r="J345" s="2" t="inlineStr"/>
+      <c r="K345" s="2" t="inlineStr"/>
+      <c r="L345" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M345" s="2" t="inlineStr"/>
+      <c r="N345" s="2" t="inlineStr">
+        <is>
+          <t>info@potio.fi</t>
+        </is>
+      </c>
+      <c r="O345" s="2" t="inlineStr"/>
+      <c r="P345" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q345" s="2" t="inlineStr">
+        <is>
+          <t>27962314</t>
+        </is>
+      </c>
+      <c r="R345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/potio-oy/</t>
+        </is>
+      </c>
+      <c r="S345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/potiofi#</t>
+        </is>
+      </c>
+      <c r="T345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/potio_fi/</t>
+        </is>
+      </c>
+      <c r="U345" s="2" t="inlineStr"/>
+      <c r="V345" s="2" t="inlineStr"/>
+      <c r="W345" s="2" t="inlineStr">
+        <is>
+          <t>Timo Kovanen</t>
+        </is>
+      </c>
+      <c r="X345" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="Y345" s="2" t="inlineStr"/>
+      <c r="Z345" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timokovanen</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>146090</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>4 Linnanherrankuja</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>00950</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>https://potio.fi</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="inlineStr"/>
+      <c r="K346" s="2" t="inlineStr"/>
+      <c r="L346" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M346" s="2" t="inlineStr"/>
+      <c r="N346" s="2" t="inlineStr">
+        <is>
+          <t>info@potio.fi</t>
+        </is>
+      </c>
+      <c r="O346" s="2" t="inlineStr"/>
+      <c r="P346" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q346" s="2" t="inlineStr">
+        <is>
+          <t>27962314</t>
+        </is>
+      </c>
+      <c r="R346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/potio-oy/</t>
+        </is>
+      </c>
+      <c r="S346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/potiofi#</t>
+        </is>
+      </c>
+      <c r="T346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/potio_fi/</t>
+        </is>
+      </c>
+      <c r="U346" s="2" t="inlineStr"/>
+      <c r="V346" s="2" t="inlineStr"/>
+      <c r="W346" s="2" t="inlineStr">
+        <is>
+          <t>Anton Molin</t>
+        </is>
+      </c>
+      <c r="X346" s="2" t="inlineStr">
+        <is>
+          <t>Import &amp; Export</t>
+        </is>
+      </c>
+      <c r="Y346" s="2" t="inlineStr"/>
+      <c r="Z346" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anton-molin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>Potio Oy</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>146090</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>4 Linnanherrankuja</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>00950</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>https://potio.fi</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="inlineStr"/>
+      <c r="K347" s="2" t="inlineStr"/>
+      <c r="L347" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M347" s="2" t="inlineStr"/>
+      <c r="N347" s="2" t="inlineStr">
+        <is>
+          <t>info@potio.fi</t>
+        </is>
+      </c>
+      <c r="O347" s="2" t="inlineStr"/>
+      <c r="P347" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q347" s="2" t="inlineStr">
+        <is>
+          <t>27962314</t>
+        </is>
+      </c>
+      <c r="R347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/potio-oy/</t>
+        </is>
+      </c>
+      <c r="S347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/potiofi#</t>
+        </is>
+      </c>
+      <c r="T347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/potio_fi/</t>
+        </is>
+      </c>
+      <c r="U347" s="2" t="inlineStr"/>
+      <c r="V347" s="2" t="inlineStr"/>
+      <c r="W347" s="2" t="inlineStr">
+        <is>
+          <t>Tom Molin</t>
+        </is>
+      </c>
+      <c r="X347" s="2" t="inlineStr">
+        <is>
+          <t>Senior Wine Director</t>
+        </is>
+      </c>
+      <c r="Y347" s="2" t="inlineStr"/>
+      <c r="Z347" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tom-molin-1162474/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
